--- a/testdata/import/03-catalog-other-headers.xlsx
+++ b/testdata/import/03-catalog-other-headers.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -434,12 +434,13 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,30 +471,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Программа</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Дата подписания лицензии</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Срок лицензии</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Статус передачи</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Менеджер</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Ответственный от вуза</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -525,23 +531,28 @@
           <t>Postgres Pro Enterprise</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Инженер данных</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>46267</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>2027</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Семёнов Максим Ильич</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Гаврилов Сергей Сергеевич</t>
         </is>
@@ -573,28 +584,33 @@
           <t>Симулятор сетевой инфраструктуры</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Инженер сетей связи</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2027</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Алексеева Юлия Романовна</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Афанасьева Екатерина Геннадьевна</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Кампус на острове Русский</t>
         </is>
@@ -626,23 +642,28 @@
           <t>Платформа онлайн-обучения</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Аналитик данных</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>46277</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Захарова Светлана Юрьевна</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Калинина Ольга Ивановна</t>
         </is>
@@ -674,23 +695,28 @@
           <t>РЕД ОС</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Администратор Linux</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>46273</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>2027</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Зайцев Артём Денисович</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Афанасьева Алла Александровна</t>
         </is>
@@ -722,23 +748,28 @@
           <t>Платформа онлайн-обучения</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Frontend-разработчик</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>46268</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>2027</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Белова Ксения Александровна</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Гусев Николай Рашидович</t>
         </is>
@@ -770,28 +801,33 @@
           <t>Песочница DevOps</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Инженер DevOps</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>46279</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>2027</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Волков Андрей Михайлович</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Гусева Анна Анатольевна</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Второй поток по DevOps</t>
         </is>
